--- a/Result/checksun_type/記憶體.xlsx
+++ b/Result/checksun_type/記憶體.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI166"/>
+  <dimension ref="A1:CI176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71975,6 +71975,4316 @@
         </is>
       </c>
       <c r="CI166" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>-6.5</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>34688.969</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>8.91</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>-7.73</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2025-09-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>2025-06-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>2025-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>19.55</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>197.04</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>3.84</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>5.42</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>-1.12</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr"/>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>45242</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>60.87</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>85.22</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>-5.10</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>15.99</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>32.86</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>26.67</t>
+        </is>
+      </c>
+      <c r="AL167" t="inlineStr">
+        <is>
+          <t>63.54</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>54.78</t>
+        </is>
+      </c>
+      <c r="AN167" t="inlineStr">
+        <is>
+          <t>41.23</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>32.55</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>6.46</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>6.38</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>6.38</t>
+        </is>
+      </c>
+      <c r="AT167" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>2328263483.926194</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>2099875179.0</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>2111858895.4</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>2288857505.6</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>9636814061.42</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>-176998610</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>-1532373820.735274</t>
+        </is>
+      </c>
+      <c r="BC167" t="n">
+        <v>-1287431861.24</v>
+      </c>
+      <c r="BD167" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BE167" t="inlineStr">
+        <is>
+          <t>19.95</t>
+        </is>
+      </c>
+      <c r="BF167" t="inlineStr">
+        <is>
+          <t>2025/09/02</t>
+        </is>
+      </c>
+      <c r="BG167" t="inlineStr">
+        <is>
+          <t>202.26</t>
+        </is>
+      </c>
+      <c r="BH167" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="BI167" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="BJ167" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BK167" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL167" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="BM167" t="inlineStr">
+        <is>
+          <t>3.850832238034093</t>
+        </is>
+      </c>
+      <c r="BN167" t="inlineStr">
+        <is>
+          <t>34.88485055211223</t>
+        </is>
+      </c>
+      <c r="BO167" t="inlineStr">
+        <is>
+          <t>2.884257801593289</t>
+        </is>
+      </c>
+      <c r="BP167" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ167" t="inlineStr">
+        <is>
+          <t>價跌量-</t>
+        </is>
+      </c>
+      <c r="BR167" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="BS167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT167" t="inlineStr">
+        <is>
+          <t>4.84</t>
+        </is>
+      </c>
+      <c r="BU167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV167" t="inlineStr">
+        <is>
+          <t>46.69%</t>
+        </is>
+      </c>
+      <c r="BW167" t="inlineStr">
+        <is>
+          <t>17.01%</t>
+        </is>
+      </c>
+      <c r="BX167" t="inlineStr">
+        <is>
+          <t>142.8</t>
+        </is>
+      </c>
+      <c r="BY167" t="inlineStr">
+        <is>
+          <t>297900</t>
+        </is>
+      </c>
+      <c r="BZ167" t="inlineStr">
+        <is>
+          <t>邏輯產品38.83%、快閃記憶體產品35.23%、客製化記憶體23.82%、其他2.13% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA167" t="inlineStr">
+        <is>
+          <t>華邦電-半導體業-上市</t>
+        </is>
+      </c>
+      <c r="CB167" t="inlineStr">
+        <is>
+          <t>半導體業右上上市</t>
+        </is>
+      </c>
+      <c r="CC167" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="CD167" t="inlineStr">
+        <is>
+          <t>62.2</t>
+        </is>
+      </c>
+      <c r="CE167" t="inlineStr">
+        <is>
+          <t>59.1</t>
+        </is>
+      </c>
+      <c r="CF167" t="inlineStr">
+        <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="CG167" t="inlineStr">
+        <is>
+          <t>21.08</t>
+        </is>
+      </c>
+      <c r="CH167" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 記憶體** 通信網路 - 記憶體** 半導體 - 記憶體IC、晶圓製造、DRAM製造</t>
+        </is>
+      </c>
+      <c r="CI167" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>-0.91</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>32553.424</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>64.2</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>-18.11</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2025-09-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>2025-06-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>2025-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>19.55</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>216.26</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>3.84</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>5.08</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>-3.58</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr"/>
+      <c r="AD168" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>45242</t>
+        </is>
+      </c>
+      <c r="AF168" t="inlineStr">
+        <is>
+          <t>94.78</t>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>98.26</t>
+        </is>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>16.92</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>33.47</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>26.30</t>
+        </is>
+      </c>
+      <c r="AL168" t="inlineStr">
+        <is>
+          <t>63.1</t>
+        </is>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t>53.97</t>
+        </is>
+      </c>
+      <c r="AN168" t="inlineStr">
+        <is>
+          <t>40.43</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>32.01</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>7.87</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>6.35</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>6.38</t>
+        </is>
+      </c>
+      <c r="AT168" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>2328263483.926194</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>2113654634.0</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>1958921858.2</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>2392088565.5</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>9626635408.0</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>-433166707</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>-1576908722.461611</t>
+        </is>
+      </c>
+      <c r="BC168" t="n">
+        <v>-1418891423.42</v>
+      </c>
+      <c r="BD168" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BE168" t="inlineStr">
+        <is>
+          <t>19.95</t>
+        </is>
+      </c>
+      <c r="BF168" t="inlineStr">
+        <is>
+          <t>2025/09/02</t>
+        </is>
+      </c>
+      <c r="BG168" t="inlineStr">
+        <is>
+          <t>221.80</t>
+        </is>
+      </c>
+      <c r="BH168" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="BI168" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="BJ168" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BK168" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL168" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="BM168" t="inlineStr">
+        <is>
+          <t>3.850832238034093</t>
+        </is>
+      </c>
+      <c r="BN168" t="inlineStr">
+        <is>
+          <t>34.88485055211223</t>
+        </is>
+      </c>
+      <c r="BO168" t="inlineStr">
+        <is>
+          <t>2.884257801593289</t>
+        </is>
+      </c>
+      <c r="BP168" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ168" t="inlineStr">
+        <is>
+          <t>價跌量-</t>
+        </is>
+      </c>
+      <c r="BR168" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="BS168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT168" t="inlineStr">
+        <is>
+          <t>4.84</t>
+        </is>
+      </c>
+      <c r="BU168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV168" t="inlineStr">
+        <is>
+          <t>46.69%</t>
+        </is>
+      </c>
+      <c r="BW168" t="inlineStr">
+        <is>
+          <t>17.01%</t>
+        </is>
+      </c>
+      <c r="BX168" t="inlineStr">
+        <is>
+          <t>142.8</t>
+        </is>
+      </c>
+      <c r="BY168" t="inlineStr">
+        <is>
+          <t>297900</t>
+        </is>
+      </c>
+      <c r="BZ168" t="inlineStr">
+        <is>
+          <t>邏輯產品38.83%、快閃記憶體產品35.23%、客製化記憶體23.82%、其他2.13% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA168" t="inlineStr">
+        <is>
+          <t>華邦電-半導體業-上市</t>
+        </is>
+      </c>
+      <c r="CB168" t="inlineStr">
+        <is>
+          <t>半導體業右上上市</t>
+        </is>
+      </c>
+      <c r="CC168" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="CD168" t="inlineStr">
+        <is>
+          <t>69.1</t>
+        </is>
+      </c>
+      <c r="CE168" t="inlineStr">
+        <is>
+          <t>61.7</t>
+        </is>
+      </c>
+      <c r="CF168" t="inlineStr">
+        <is>
+          <t>64.2</t>
+        </is>
+      </c>
+      <c r="CG168" t="inlineStr">
+        <is>
+          <t>21.08</t>
+        </is>
+      </c>
+      <c r="CH168" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 記憶體** 通信網路 - 記憶體** 半導體 - 記憶體IC、晶圓製造、DRAM製造</t>
+        </is>
+      </c>
+      <c r="CI168" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>23237.65</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>64.8</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>-22.19</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2025-09-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>2025-06-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>2025-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>19.55</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>219.21</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>3.84</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>3.63</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr"/>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>45242</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>4.42</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>17.63</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>33.42</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>25.80</t>
+        </is>
+      </c>
+      <c r="AL169" t="inlineStr">
+        <is>
+          <t>62.06</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>52.76</t>
+        </is>
+      </c>
+      <c r="AN169" t="inlineStr">
+        <is>
+          <t>39.54</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>31.43</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>10.03</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>6.23</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>6.38</t>
+        </is>
+      </c>
+      <c r="AT169" t="inlineStr">
+        <is>
+          <t>-2.31</t>
+        </is>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="AV169" t="inlineStr">
+        <is>
+          <t>2328263483.926194</t>
+        </is>
+      </c>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>1500955259.0</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>2015563385.4</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr">
+        <is>
+          <t>2590389016.0</t>
+        </is>
+      </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>9617543062.1</t>
+        </is>
+      </c>
+      <c r="BA169" t="inlineStr">
+        <is>
+          <t>-574825630</t>
+        </is>
+      </c>
+      <c r="BB169" t="inlineStr">
+        <is>
+          <t>-1605639140.468955</t>
+        </is>
+      </c>
+      <c r="BC169" t="n">
+        <v>-1557492474.45</v>
+      </c>
+      <c r="BD169" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BE169" t="inlineStr">
+        <is>
+          <t>19.95</t>
+        </is>
+      </c>
+      <c r="BF169" t="inlineStr">
+        <is>
+          <t>2025/09/02</t>
+        </is>
+      </c>
+      <c r="BG169" t="inlineStr">
+        <is>
+          <t>224.81</t>
+        </is>
+      </c>
+      <c r="BH169" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="BI169" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="BJ169" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BK169" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL169" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="BM169" t="inlineStr">
+        <is>
+          <t>3.850832238034093</t>
+        </is>
+      </c>
+      <c r="BN169" t="inlineStr">
+        <is>
+          <t>34.88485055211223</t>
+        </is>
+      </c>
+      <c r="BO169" t="inlineStr">
+        <is>
+          <t>2.884257801593289</t>
+        </is>
+      </c>
+      <c r="BP169" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ169" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR169" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="BS169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT169" t="inlineStr">
+        <is>
+          <t>4.84</t>
+        </is>
+      </c>
+      <c r="BU169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV169" t="inlineStr">
+        <is>
+          <t>46.69%</t>
+        </is>
+      </c>
+      <c r="BW169" t="inlineStr">
+        <is>
+          <t>17.01%</t>
+        </is>
+      </c>
+      <c r="BX169" t="inlineStr">
+        <is>
+          <t>142.8</t>
+        </is>
+      </c>
+      <c r="BY169" t="inlineStr">
+        <is>
+          <t>297900</t>
+        </is>
+      </c>
+      <c r="BZ169" t="inlineStr">
+        <is>
+          <t>邏輯產品38.83%、快閃記憶體產品35.23%、客製化記憶體23.82%、其他2.13% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA169" t="inlineStr">
+        <is>
+          <t>華邦電-半導體業-上市</t>
+        </is>
+      </c>
+      <c r="CB169" t="inlineStr">
+        <is>
+          <t>半導體業右上上市</t>
+        </is>
+      </c>
+      <c r="CC169" t="inlineStr">
+        <is>
+          <t>63.1</t>
+        </is>
+      </c>
+      <c r="CD169" t="inlineStr">
+        <is>
+          <t>65.9</t>
+        </is>
+      </c>
+      <c r="CE169" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="CF169" t="inlineStr">
+        <is>
+          <t>64.8</t>
+        </is>
+      </c>
+      <c r="CG169" t="inlineStr">
+        <is>
+          <t>21.08</t>
+        </is>
+      </c>
+      <c r="CH169" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 記憶體** 通信網路 - 記憶體** 半導體 - 記憶體IC、晶圓製造、DRAM製造</t>
+        </is>
+      </c>
+      <c r="CI169" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>43521.354</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>64.5</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>-21.62</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2025-09-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>2025-06-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>2025-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>19.55</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>217.73</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>3.84</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>6.80</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>-2.48</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr"/>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>45242</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>94.74</t>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>6.97</t>
+        </is>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>16.97</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>33.42</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>25.26</t>
+        </is>
+      </c>
+      <c r="AL170" t="inlineStr">
+        <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>51.55</t>
+        </is>
+      </c>
+      <c r="AN170" t="inlineStr">
+        <is>
+          <t>38.64</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>30.85</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>10.19</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>6.69</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>6.07</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>6.38</t>
+        </is>
+      </c>
+      <c r="AT170" t="inlineStr">
+        <is>
+          <t>-4.76</t>
+        </is>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr">
+        <is>
+          <t>2328263483.926194</t>
+        </is>
+      </c>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>2838761748.0</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>2210865487.2</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>2820810160.0</t>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>9609060956.48</t>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>-609944672</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>-1614393079.745097</t>
+        </is>
+      </c>
+      <c r="BC170" t="n">
+        <v>-1634222883.08</v>
+      </c>
+      <c r="BD170" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BE170" t="inlineStr">
+        <is>
+          <t>19.95</t>
+        </is>
+      </c>
+      <c r="BF170" t="inlineStr">
+        <is>
+          <t>2025/09/02</t>
+        </is>
+      </c>
+      <c r="BG170" t="inlineStr">
+        <is>
+          <t>223.31</t>
+        </is>
+      </c>
+      <c r="BH170" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="BI170" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="BJ170" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BK170" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL170" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="BM170" t="inlineStr">
+        <is>
+          <t>3.850832238034093</t>
+        </is>
+      </c>
+      <c r="BN170" t="inlineStr">
+        <is>
+          <t>34.88485055211223</t>
+        </is>
+      </c>
+      <c r="BO170" t="inlineStr">
+        <is>
+          <t>2.884257801593289</t>
+        </is>
+      </c>
+      <c r="BP170" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ170" t="inlineStr">
+        <is>
+          <t>價跌量-</t>
+        </is>
+      </c>
+      <c r="BR170" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="BS170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT170" t="inlineStr">
+        <is>
+          <t>4.84</t>
+        </is>
+      </c>
+      <c r="BU170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV170" t="inlineStr">
+        <is>
+          <t>46.69%</t>
+        </is>
+      </c>
+      <c r="BW170" t="inlineStr">
+        <is>
+          <t>17.01%</t>
+        </is>
+      </c>
+      <c r="BX170" t="inlineStr">
+        <is>
+          <t>142.8</t>
+        </is>
+      </c>
+      <c r="BY170" t="inlineStr">
+        <is>
+          <t>297900</t>
+        </is>
+      </c>
+      <c r="BZ170" t="inlineStr">
+        <is>
+          <t>邏輯產品38.83%、快閃記憶體產品35.23%、客製化記憶體23.82%、其他2.13% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA170" t="inlineStr">
+        <is>
+          <t>華邦電-半導體業-上市</t>
+        </is>
+      </c>
+      <c r="CB170" t="inlineStr">
+        <is>
+          <t>半導體業右上上市</t>
+        </is>
+      </c>
+      <c r="CC170" t="inlineStr">
+        <is>
+          <t>64.9</t>
+        </is>
+      </c>
+      <c r="CD170" t="inlineStr">
+        <is>
+          <t>66.1</t>
+        </is>
+      </c>
+      <c r="CE170" t="inlineStr">
+        <is>
+          <t>64.5</t>
+        </is>
+      </c>
+      <c r="CF170" t="inlineStr">
+        <is>
+          <t>64.5</t>
+        </is>
+      </c>
+      <c r="CG170" t="inlineStr">
+        <is>
+          <t>21.08</t>
+        </is>
+      </c>
+      <c r="CH170" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 記憶體** 通信網路 - 記憶體** 半導體 - 記憶體IC、晶圓製造、DRAM製造</t>
+        </is>
+      </c>
+      <c r="CI170" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>9.45</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>32006.484</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>63.9</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>-31.58</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2025-09-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>2025-06-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>2025-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>19.55</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>214.78</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>3.84</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>5.10</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr"/>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>45242</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>94.74</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>15.02</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>33.73</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>24.73</t>
+        </is>
+      </c>
+      <c r="AL171" t="inlineStr">
+        <is>
+          <t>58.06</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>50.48</t>
+        </is>
+      </c>
+      <c r="AN171" t="inlineStr">
+        <is>
+          <t>37.74</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>30.26</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>6.42</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>5.92</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>6.38</t>
+        </is>
+      </c>
+      <c r="AT171" t="inlineStr">
+        <is>
+          <t>-7.19</t>
+        </is>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="AV171" t="inlineStr">
+        <is>
+          <t>2328263483.926194</t>
+        </is>
+      </c>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>2006047657.0</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>2091634540.2</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>3057055845.2</t>
+        </is>
+      </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>9589791529.6</t>
+        </is>
+      </c>
+      <c r="BA171" t="inlineStr">
+        <is>
+          <t>-965421304</t>
+        </is>
+      </c>
+      <c r="BB171" t="inlineStr">
+        <is>
+          <t>-1610787660.95646</t>
+        </is>
+      </c>
+      <c r="BC171" t="n">
+        <v>-1828809059.13</v>
+      </c>
+      <c r="BD171" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BE171" t="inlineStr">
+        <is>
+          <t>19.95</t>
+        </is>
+      </c>
+      <c r="BF171" t="inlineStr">
+        <is>
+          <t>2025/09/02</t>
+        </is>
+      </c>
+      <c r="BG171" t="inlineStr">
+        <is>
+          <t>220.30</t>
+        </is>
+      </c>
+      <c r="BH171" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="BI171" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="BJ171" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BK171" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL171" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="BM171" t="inlineStr">
+        <is>
+          <t>3.850832238034093</t>
+        </is>
+      </c>
+      <c r="BN171" t="inlineStr">
+        <is>
+          <t>34.88485055211223</t>
+        </is>
+      </c>
+      <c r="BO171" t="inlineStr">
+        <is>
+          <t>2.884257801593289</t>
+        </is>
+      </c>
+      <c r="BP171" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ171" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BR171" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="BS171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT171" t="inlineStr">
+        <is>
+          <t>4.84</t>
+        </is>
+      </c>
+      <c r="BU171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV171" t="inlineStr">
+        <is>
+          <t>46.69%</t>
+        </is>
+      </c>
+      <c r="BW171" t="inlineStr">
+        <is>
+          <t>17.01%</t>
+        </is>
+      </c>
+      <c r="BX171" t="inlineStr">
+        <is>
+          <t>142.8</t>
+        </is>
+      </c>
+      <c r="BY171" t="inlineStr">
+        <is>
+          <t>297900</t>
+        </is>
+      </c>
+      <c r="BZ171" t="inlineStr">
+        <is>
+          <t>邏輯產品38.83%、快閃記憶體產品35.23%、客製化記憶體23.82%、其他2.13% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA171" t="inlineStr">
+        <is>
+          <t>華邦電-半導體業-上市</t>
+        </is>
+      </c>
+      <c r="CB171" t="inlineStr">
+        <is>
+          <t>半導體業右上上市</t>
+        </is>
+      </c>
+      <c r="CC171" t="inlineStr">
+        <is>
+          <t>61.4</t>
+        </is>
+      </c>
+      <c r="CD171" t="inlineStr">
+        <is>
+          <t>63.9</t>
+        </is>
+      </c>
+      <c r="CE171" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="CF171" t="inlineStr">
+        <is>
+          <t>63.9</t>
+        </is>
+      </c>
+      <c r="CG171" t="inlineStr">
+        <is>
+          <t>21.08</t>
+        </is>
+      </c>
+      <c r="CH171" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 記憶體** 通信網路 - 記憶體** 半導體 - 記憶體IC、晶圓製造、DRAM製造</t>
+        </is>
+      </c>
+      <c r="CI171" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>-1.54</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>22850.042</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>12.24</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>-25.08</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2025-09-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>2025-06-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>2025-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>19.55</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>186.21</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>3.84</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>-1.03</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr"/>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>45242</t>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t>84.21</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>92.8</t>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>34.24</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>24.11</t>
+        </is>
+      </c>
+      <c r="AL172" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="AM172" t="inlineStr">
+        <is>
+          <t>49.46</t>
+        </is>
+      </c>
+      <c r="AN172" t="inlineStr">
+        <is>
+          <t>36.84</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>29.69</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>4.21</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>6.04</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>5.79</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>6.38</t>
+        </is>
+      </c>
+      <c r="AT172" t="inlineStr">
+        <is>
+          <t>-9.15</t>
+        </is>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t>2328263483.926194</t>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>1335189993.0</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>2465856115.8</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t>3291201848.1</t>
+        </is>
+      </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>9561071508.76</t>
+        </is>
+      </c>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>-825345732</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t>-1571147406.74382</t>
+        </is>
+      </c>
+      <c r="BC172" t="n">
+        <v>-1952255334.47</v>
+      </c>
+      <c r="BD172" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BE172" t="inlineStr">
+        <is>
+          <t>19.95</t>
+        </is>
+      </c>
+      <c r="BF172" t="inlineStr">
+        <is>
+          <t>2025/09/02</t>
+        </is>
+      </c>
+      <c r="BG172" t="inlineStr">
+        <is>
+          <t>191.23</t>
+        </is>
+      </c>
+      <c r="BH172" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="BI172" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="BJ172" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BK172" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL172" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="BM172" t="inlineStr">
+        <is>
+          <t>3.850832238034093</t>
+        </is>
+      </c>
+      <c r="BN172" t="inlineStr">
+        <is>
+          <t>34.88485055211223</t>
+        </is>
+      </c>
+      <c r="BO172" t="inlineStr">
+        <is>
+          <t>2.884257801593289</t>
+        </is>
+      </c>
+      <c r="BP172" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ172" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BR172" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="BS172" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT172" t="inlineStr">
+        <is>
+          <t>4.84</t>
+        </is>
+      </c>
+      <c r="BU172" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV172" t="inlineStr">
+        <is>
+          <t>46.69%</t>
+        </is>
+      </c>
+      <c r="BW172" t="inlineStr">
+        <is>
+          <t>17.01%</t>
+        </is>
+      </c>
+      <c r="BX172" t="inlineStr">
+        <is>
+          <t>142.8</t>
+        </is>
+      </c>
+      <c r="BY172" t="inlineStr">
+        <is>
+          <t>297900</t>
+        </is>
+      </c>
+      <c r="BZ172" t="inlineStr">
+        <is>
+          <t>邏輯產品38.83%、快閃記憶體產品35.23%、客製化記憶體23.82%、其他2.13% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA172" t="inlineStr">
+        <is>
+          <t>華邦電-半導體業-上市</t>
+        </is>
+      </c>
+      <c r="CB172" t="inlineStr">
+        <is>
+          <t>半導體業右上上市</t>
+        </is>
+      </c>
+      <c r="CC172" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="CD172" t="inlineStr">
+        <is>
+          <t>59.2</t>
+        </is>
+      </c>
+      <c r="CE172" t="inlineStr">
+        <is>
+          <t>57.6</t>
+        </is>
+      </c>
+      <c r="CF172" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="CG172" t="inlineStr">
+        <is>
+          <t>21.08</t>
+        </is>
+      </c>
+      <c r="CH172" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 記憶體** 通信網路 - 記憶體** 半導體 - 記憶體IC、晶圓製造、DRAM製造</t>
+        </is>
+      </c>
+      <c r="CI172" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>5.12</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>40871.416</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>10.88</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>-16.05</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2025-09-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>2025-06-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>2025-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>19.55</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>190.64</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>3.84</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>6.38</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr"/>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>45242</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>88.19</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>5.70</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>14.83</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>34.85</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>23.50</t>
+        </is>
+      </c>
+      <c r="AL173" t="inlineStr">
+        <is>
+          <t>55.82000000000001</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>48.61</t>
+        </is>
+      </c>
+      <c r="AN173" t="inlineStr">
+        <is>
+          <t>36.05</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>29.19</t>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t>5.61</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>6.05</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>5.73</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>6.38</t>
+        </is>
+      </c>
+      <c r="AT173" t="inlineStr">
+        <is>
+          <t>-10.10</t>
+        </is>
+      </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="AV173" t="inlineStr">
+        <is>
+          <t>2328263483.926194</t>
+        </is>
+      </c>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>2396862270.0</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>2825255272.8</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t>3365323039.3</t>
+        </is>
+      </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>9545252267.34</t>
+        </is>
+      </c>
+      <c r="BA173" t="inlineStr">
+        <is>
+          <t>-540067766</t>
+        </is>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>-1501855056.248303</t>
+        </is>
+      </c>
+      <c r="BC173" t="n">
+        <v>-1987006144.73</v>
+      </c>
+      <c r="BD173" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BE173" t="inlineStr">
+        <is>
+          <t>19.95</t>
+        </is>
+      </c>
+      <c r="BF173" t="inlineStr">
+        <is>
+          <t>2025/09/02</t>
+        </is>
+      </c>
+      <c r="BG173" t="inlineStr">
+        <is>
+          <t>195.74</t>
+        </is>
+      </c>
+      <c r="BH173" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="BI173" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="BJ173" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BK173" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL173" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="BM173" t="inlineStr">
+        <is>
+          <t>3.850832238034093</t>
+        </is>
+      </c>
+      <c r="BN173" t="inlineStr">
+        <is>
+          <t>34.88485055211223</t>
+        </is>
+      </c>
+      <c r="BO173" t="inlineStr">
+        <is>
+          <t>2.884257801593289</t>
+        </is>
+      </c>
+      <c r="BP173" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ173" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR173" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="BS173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT173" t="inlineStr">
+        <is>
+          <t>4.84</t>
+        </is>
+      </c>
+      <c r="BU173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV173" t="inlineStr">
+        <is>
+          <t>46.69%</t>
+        </is>
+      </c>
+      <c r="BW173" t="inlineStr">
+        <is>
+          <t>17.01%</t>
+        </is>
+      </c>
+      <c r="BX173" t="inlineStr">
+        <is>
+          <t>142.8</t>
+        </is>
+      </c>
+      <c r="BY173" t="inlineStr">
+        <is>
+          <t>297900</t>
+        </is>
+      </c>
+      <c r="BZ173" t="inlineStr">
+        <is>
+          <t>邏輯產品38.83%、快閃記憶體產品35.23%、客製化記憶體23.82%、其他2.13% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA173" t="inlineStr">
+        <is>
+          <t>華邦電-半導體業-上市</t>
+        </is>
+      </c>
+      <c r="CB173" t="inlineStr">
+        <is>
+          <t>半導體業右上上市</t>
+        </is>
+      </c>
+      <c r="CC173" t="inlineStr">
+        <is>
+          <t>58.6</t>
+        </is>
+      </c>
+      <c r="CD173" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="CE173" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
+      </c>
+      <c r="CF173" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="CG173" t="inlineStr">
+        <is>
+          <t>21.08</t>
+        </is>
+      </c>
+      <c r="CH173" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 記憶體** 通信網路 - 記憶體** 半導體 - 記憶體IC、晶圓製造、DRAM製造</t>
+        </is>
+      </c>
+      <c r="CI173" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>5.56</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>47931.403</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>56.0</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>15.41</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>-6.22</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2025-09-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>2025-06-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>2025-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>19.55</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>175.86</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>3.84</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>7.48</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>15.23</t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr"/>
+      <c r="AD174" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t>45242</t>
+        </is>
+      </c>
+      <c r="AF174" t="inlineStr">
+        <is>
+          <t>94.17</t>
+        </is>
+      </c>
+      <c r="AG174" t="inlineStr">
+        <is>
+          <t>88.19</t>
+        </is>
+      </c>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="AI174" t="inlineStr">
+        <is>
+          <t>15.20</t>
+        </is>
+      </c>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>35.66</t>
+        </is>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>22.84</t>
+        </is>
+      </c>
+      <c r="AL174" t="inlineStr">
+        <is>
+          <t>55.06</t>
+        </is>
+      </c>
+      <c r="AM174" t="inlineStr">
+        <is>
+          <t>47.8</t>
+        </is>
+      </c>
+      <c r="AN174" t="inlineStr">
+        <is>
+          <t>35.23</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>28.68</t>
+        </is>
+      </c>
+      <c r="AP174" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="AQ174" t="inlineStr">
+        <is>
+          <t>5.89</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>5.65</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr">
+        <is>
+          <t>6.38</t>
+        </is>
+      </c>
+      <c r="AT174" t="inlineStr">
+        <is>
+          <t>-11.36</t>
+        </is>
+      </c>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="AV174" t="inlineStr">
+        <is>
+          <t>2328263483.926194</t>
+        </is>
+      </c>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>2477465768.0</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>3165214646.6</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t>3374978832.8</t>
+        </is>
+      </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>9504029463.98</t>
+        </is>
+      </c>
+      <c r="BA174" t="inlineStr">
+        <is>
+          <t>-209764186</t>
+        </is>
+      </c>
+      <c r="BB174" t="inlineStr">
+        <is>
+          <t>-1413645767.433743</t>
+        </is>
+      </c>
+      <c r="BC174" t="n">
+        <v>-2079436255.32</v>
+      </c>
+      <c r="BD174" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BE174" t="inlineStr">
+        <is>
+          <t>19.95</t>
+        </is>
+      </c>
+      <c r="BF174" t="inlineStr">
+        <is>
+          <t>2025/09/02</t>
+        </is>
+      </c>
+      <c r="BG174" t="inlineStr">
+        <is>
+          <t>180.70</t>
+        </is>
+      </c>
+      <c r="BH174" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="BI174" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="BJ174" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BK174" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL174" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="BM174" t="inlineStr">
+        <is>
+          <t>3.850832238034093</t>
+        </is>
+      </c>
+      <c r="BN174" t="inlineStr">
+        <is>
+          <t>34.88485055211223</t>
+        </is>
+      </c>
+      <c r="BO174" t="inlineStr">
+        <is>
+          <t>2.884257801593289</t>
+        </is>
+      </c>
+      <c r="BP174" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ174" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="BR174" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="BS174" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT174" t="inlineStr">
+        <is>
+          <t>4.84</t>
+        </is>
+      </c>
+      <c r="BU174" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV174" t="inlineStr">
+        <is>
+          <t>46.69%</t>
+        </is>
+      </c>
+      <c r="BW174" t="inlineStr">
+        <is>
+          <t>17.01%</t>
+        </is>
+      </c>
+      <c r="BX174" t="inlineStr">
+        <is>
+          <t>142.8</t>
+        </is>
+      </c>
+      <c r="BY174" t="inlineStr">
+        <is>
+          <t>297900</t>
+        </is>
+      </c>
+      <c r="BZ174" t="inlineStr">
+        <is>
+          <t>邏輯產品38.83%、快閃記憶體產品35.23%、客製化記憶體23.82%、其他2.13% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA174" t="inlineStr">
+        <is>
+          <t>華邦電-半導體業-上市</t>
+        </is>
+      </c>
+      <c r="CB174" t="inlineStr">
+        <is>
+          <t>半導體業右上上市</t>
+        </is>
+      </c>
+      <c r="CC174" t="inlineStr">
+        <is>
+          <t>48.6</t>
+        </is>
+      </c>
+      <c r="CD174" t="inlineStr">
+        <is>
+          <t>56.0</t>
+        </is>
+      </c>
+      <c r="CE174" t="inlineStr">
+        <is>
+          <t>48.6</t>
+        </is>
+      </c>
+      <c r="CF174" t="inlineStr">
+        <is>
+          <t>56.0</t>
+        </is>
+      </c>
+      <c r="CG174" t="inlineStr">
+        <is>
+          <t>21.08</t>
+        </is>
+      </c>
+      <c r="CH174" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 記憶體** 通信網路 - 記憶體** 半導體 - 記憶體IC、晶圓製造、DRAM製造</t>
+        </is>
+      </c>
+      <c r="CI174" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>-5.81</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>41115.669</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>19.49</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>-1.38</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2025-09-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>2025-06-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>2025-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>19.55</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>162.56</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>3.84</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>6.42</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>-6.00</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr"/>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>45242</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>70.4</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>86.99</t>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>-2.49</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>16.46</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>36.12</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>22.22</t>
+        </is>
+      </c>
+      <c r="AL175" t="inlineStr">
+        <is>
+          <t>54.66</t>
+        </is>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t>46.94</t>
+        </is>
+      </c>
+      <c r="AN175" t="inlineStr">
+        <is>
+          <t>34.48</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>28.21</t>
+        </is>
+      </c>
+      <c r="AP175" t="inlineStr">
+        <is>
+          <t>5.73</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>5.91</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>5.59</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>6.38</t>
+        </is>
+      </c>
+      <c r="AT175" t="inlineStr">
+        <is>
+          <t>-12.31</t>
+        </is>
+      </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="AV175" t="inlineStr">
+        <is>
+          <t>2328263483.926194</t>
+        </is>
+      </c>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>2242607013.0</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>3430754832.8</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr">
+        <is>
+          <t>3478589163.1</t>
+        </is>
+      </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>9467389937.38</t>
+        </is>
+      </c>
+      <c r="BA175" t="inlineStr">
+        <is>
+          <t>-47834330</t>
+        </is>
+      </c>
+      <c r="BB175" t="inlineStr">
+        <is>
+          <t>-1292592951.453937</t>
+        </is>
+      </c>
+      <c r="BC175" t="n">
+        <v>-2145849778.98</v>
+      </c>
+      <c r="BD175" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BE175" t="inlineStr">
+        <is>
+          <t>19.95</t>
+        </is>
+      </c>
+      <c r="BF175" t="inlineStr">
+        <is>
+          <t>2025/09/02</t>
+        </is>
+      </c>
+      <c r="BG175" t="inlineStr">
+        <is>
+          <t>167.17</t>
+        </is>
+      </c>
+      <c r="BH175" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="BI175" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="BJ175" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BK175" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL175" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="BM175" t="inlineStr">
+        <is>
+          <t>3.850832238034093</t>
+        </is>
+      </c>
+      <c r="BN175" t="inlineStr">
+        <is>
+          <t>34.88485055211223</t>
+        </is>
+      </c>
+      <c r="BO175" t="inlineStr">
+        <is>
+          <t>2.884257801593289</t>
+        </is>
+      </c>
+      <c r="BP175" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ175" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR175" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="BS175" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT175" t="inlineStr">
+        <is>
+          <t>4.84</t>
+        </is>
+      </c>
+      <c r="BU175" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV175" t="inlineStr">
+        <is>
+          <t>46.69%</t>
+        </is>
+      </c>
+      <c r="BW175" t="inlineStr">
+        <is>
+          <t>17.01%</t>
+        </is>
+      </c>
+      <c r="BX175" t="inlineStr">
+        <is>
+          <t>142.8</t>
+        </is>
+      </c>
+      <c r="BY175" t="inlineStr">
+        <is>
+          <t>297900</t>
+        </is>
+      </c>
+      <c r="BZ175" t="inlineStr">
+        <is>
+          <t>邏輯產品38.83%、快閃記憶體產品35.23%、客製化記憶體23.82%、其他2.13% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA175" t="inlineStr">
+        <is>
+          <t>華邦電-半導體業-上市</t>
+        </is>
+      </c>
+      <c r="CB175" t="inlineStr">
+        <is>
+          <t>半導體業右上上市</t>
+        </is>
+      </c>
+      <c r="CC175" t="inlineStr">
+        <is>
+          <t>56.8</t>
+        </is>
+      </c>
+      <c r="CD175" t="inlineStr">
+        <is>
+          <t>56.8</t>
+        </is>
+      </c>
+      <c r="CE175" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="CF175" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
+      <c r="CG175" t="inlineStr">
+        <is>
+          <t>21.08</t>
+        </is>
+      </c>
+      <c r="CH175" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 記憶體** 通信網路 - 記憶體** 半導體 - 記憶體IC、晶圓製造、DRAM製造</t>
+        </is>
+      </c>
+      <c r="CI175" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>4.32</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>68487.857</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>14.5</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>-31.84</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2025-09-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>2025-06-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>2025-07-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>19.55</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>178.82</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>3.84</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>10.69</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr"/>
+      <c r="AD176" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>45242</t>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>96.86</t>
+        </is>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>36.41</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>21.57</t>
+        </is>
+      </c>
+      <c r="AL176" t="inlineStr">
+        <is>
+          <t>54.8</t>
+        </is>
+      </c>
+      <c r="AM176" t="inlineStr">
+        <is>
+          <t>46.07</t>
+        </is>
+      </c>
+      <c r="AN176" t="inlineStr">
+        <is>
+          <t>33.77</t>
+        </is>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t>27.78</t>
+        </is>
+      </c>
+      <c r="AP176" t="inlineStr">
+        <is>
+          <t>11.09</t>
+        </is>
+      </c>
+      <c r="AQ176" t="inlineStr">
+        <is>
+          <t>6.12</t>
+        </is>
+      </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>5.51</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr">
+        <is>
+          <t>6.38</t>
+        </is>
+      </c>
+      <c r="AT176" t="inlineStr">
+        <is>
+          <t>-13.57</t>
+        </is>
+      </c>
+      <c r="AU176" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="AV176" t="inlineStr">
+        <is>
+          <t>2328263483.926194</t>
+        </is>
+      </c>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>3877155535.0</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>4022477150.2</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr">
+        <is>
+          <t>5901932412.0</t>
+        </is>
+      </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>9439650790.64</t>
+        </is>
+      </c>
+      <c r="BA176" t="inlineStr">
+        <is>
+          <t>-1879455261</t>
+        </is>
+      </c>
+      <c r="BB176" t="inlineStr">
+        <is>
+          <t>-1137455346.44891</t>
+        </is>
+      </c>
+      <c r="BC176" t="n">
+        <v>-2138925311.21</v>
+      </c>
+      <c r="BD176" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BE176" t="inlineStr">
+        <is>
+          <t>19.95</t>
+        </is>
+      </c>
+      <c r="BF176" t="inlineStr">
+        <is>
+          <t>2025/09/02</t>
+        </is>
+      </c>
+      <c r="BG176" t="inlineStr">
+        <is>
+          <t>183.71</t>
+        </is>
+      </c>
+      <c r="BH176" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="BI176" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="BJ176" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="BK176" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL176" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="BM176" t="inlineStr">
+        <is>
+          <t>3.850832238034093</t>
+        </is>
+      </c>
+      <c r="BN176" t="inlineStr">
+        <is>
+          <t>34.88485055211223</t>
+        </is>
+      </c>
+      <c r="BO176" t="inlineStr">
+        <is>
+          <t>2.884257801593289</t>
+        </is>
+      </c>
+      <c r="BP176" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ176" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR176" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="BS176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT176" t="inlineStr">
+        <is>
+          <t>4.84</t>
+        </is>
+      </c>
+      <c r="BU176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV176" t="inlineStr">
+        <is>
+          <t>46.69%</t>
+        </is>
+      </c>
+      <c r="BW176" t="inlineStr">
+        <is>
+          <t>17.01%</t>
+        </is>
+      </c>
+      <c r="BX176" t="inlineStr">
+        <is>
+          <t>142.8</t>
+        </is>
+      </c>
+      <c r="BY176" t="inlineStr">
+        <is>
+          <t>297900</t>
+        </is>
+      </c>
+      <c r="BZ176" t="inlineStr">
+        <is>
+          <t>邏輯產品38.83%、快閃記憶體產品35.23%、客製化記憶體23.82%、其他2.13% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA176" t="inlineStr">
+        <is>
+          <t>華邦電-半導體業-上市</t>
+        </is>
+      </c>
+      <c r="CB176" t="inlineStr">
+        <is>
+          <t>半導體業右上上市</t>
+        </is>
+      </c>
+      <c r="CC176" t="inlineStr">
+        <is>
+          <t>55.5</t>
+        </is>
+      </c>
+      <c r="CD176" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
+      <c r="CE176" t="inlineStr">
+        <is>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="CF176" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CG176" t="inlineStr">
+        <is>
+          <t>21.08</t>
+        </is>
+      </c>
+      <c r="CH176" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 記憶體** 通信網路 - 記憶體** 半導體 - 記憶體IC、晶圓製造、DRAM製造</t>
+        </is>
+      </c>
+      <c r="CI176" t="inlineStr">
         <is>
           <t>False</t>
         </is>
